--- a/data/nzd0346/nzd0346.xlsx
+++ b/data/nzd0346/nzd0346.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N400"/>
+  <dimension ref="A1:N401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19652,6 +19652,54 @@
       <c r="N400" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-15 22:01:19+00:00</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>340.04</v>
+      </c>
+      <c r="C401" t="n">
+        <v>331.6</v>
+      </c>
+      <c r="D401" t="n">
+        <v>327.33</v>
+      </c>
+      <c r="E401" t="n">
+        <v>321.51</v>
+      </c>
+      <c r="F401" t="n">
+        <v>329.96</v>
+      </c>
+      <c r="G401" t="n">
+        <v>334.05</v>
+      </c>
+      <c r="H401" t="n">
+        <v>333.79</v>
+      </c>
+      <c r="I401" t="n">
+        <v>332.69</v>
+      </c>
+      <c r="J401" t="n">
+        <v>338.91</v>
+      </c>
+      <c r="K401" t="n">
+        <v>330.85</v>
+      </c>
+      <c r="L401" t="n">
+        <v>323.98</v>
+      </c>
+      <c r="M401" t="n">
+        <v>327.59</v>
+      </c>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -19666,7 +19714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B426"/>
+  <dimension ref="A1:B427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23929,6 +23977,16 @@
       </c>
       <c r="B426" t="n">
         <v>0.05</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2025-11-15 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B427" t="n">
+        <v>-0.23</v>
       </c>
     </row>
   </sheetData>
@@ -24097,28 +24155,28 @@
         <v>0.1454</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1716597481279585</v>
+        <v>-0.1717048418150572</v>
       </c>
       <c r="J2" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K2" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07207107364294019</v>
+        <v>0.07244088026262641</v>
       </c>
       <c r="M2" t="n">
-        <v>3.694995325573081</v>
+        <v>3.685987808569938</v>
       </c>
       <c r="N2" t="n">
-        <v>22.31719199200091</v>
+        <v>22.26142297101676</v>
       </c>
       <c r="O2" t="n">
-        <v>4.724107533915895</v>
+        <v>4.718201243166378</v>
       </c>
       <c r="P2" t="n">
-        <v>344.6482998574385</v>
+        <v>344.6487503018628</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24175,28 +24233,28 @@
         <v>0.1252</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1245309519107261</v>
+        <v>-0.1256765823733336</v>
       </c>
       <c r="J3" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K3" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03726006726526232</v>
+        <v>0.03808112902574479</v>
       </c>
       <c r="M3" t="n">
-        <v>3.596796376717454</v>
+        <v>3.592463939356928</v>
       </c>
       <c r="N3" t="n">
-        <v>23.57050315034712</v>
+        <v>23.52704104854575</v>
       </c>
       <c r="O3" t="n">
-        <v>4.854946256174946</v>
+        <v>4.850468126742588</v>
       </c>
       <c r="P3" t="n">
-        <v>337.3628029404152</v>
+        <v>337.3742467341596</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24253,28 +24311,28 @@
         <v>0.1507</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03736400733135194</v>
+        <v>-0.03962233068766199</v>
       </c>
       <c r="J4" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K4" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00308352971689474</v>
+        <v>0.003475636153641326</v>
       </c>
       <c r="M4" t="n">
-        <v>3.741684996203107</v>
+        <v>3.739372167429895</v>
       </c>
       <c r="N4" t="n">
-        <v>26.5501156066492</v>
+        <v>26.54383130918833</v>
       </c>
       <c r="O4" t="n">
-        <v>5.152680429315328</v>
+        <v>5.152070584647334</v>
       </c>
       <c r="P4" t="n">
-        <v>333.2303349392036</v>
+        <v>333.2528935106985</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -24331,28 +24389,28 @@
         <v>0.077</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.03014694223067014</v>
+        <v>-0.03569157998276765</v>
       </c>
       <c r="J5" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K5" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002056985481157181</v>
+        <v>0.002855343890456274</v>
       </c>
       <c r="M5" t="n">
-        <v>3.883512340172992</v>
+        <v>3.898407186787031</v>
       </c>
       <c r="N5" t="n">
-        <v>25.93641460347239</v>
+        <v>26.23380278078323</v>
       </c>
       <c r="O5" t="n">
-        <v>5.092780635710946</v>
+        <v>5.121894452327501</v>
       </c>
       <c r="P5" t="n">
-        <v>334.3885413158243</v>
+        <v>334.443927143011</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24409,28 +24467,28 @@
         <v>0.116</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06214218015609896</v>
+        <v>0.05985923065936146</v>
       </c>
       <c r="J6" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K6" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009727484689436294</v>
+        <v>0.00905313532280505</v>
       </c>
       <c r="M6" t="n">
-        <v>3.776378868418423</v>
+        <v>3.778429980677466</v>
       </c>
       <c r="N6" t="n">
-        <v>23.1246957396873</v>
+        <v>23.12829267526723</v>
       </c>
       <c r="O6" t="n">
-        <v>4.80881437983286</v>
+        <v>4.809188359304222</v>
       </c>
       <c r="P6" t="n">
-        <v>333.2994860728763</v>
+        <v>333.3222906368453</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24487,28 +24545,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1145121981565041</v>
+        <v>0.1122886290746248</v>
       </c>
       <c r="J7" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K7" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02916980826886928</v>
+        <v>0.02815381173786724</v>
       </c>
       <c r="M7" t="n">
-        <v>3.775840454221508</v>
+        <v>3.778731296773701</v>
       </c>
       <c r="N7" t="n">
-        <v>25.67214094590914</v>
+        <v>25.6662162863294</v>
       </c>
       <c r="O7" t="n">
-        <v>5.066768294081459</v>
+        <v>5.066183601719287</v>
       </c>
       <c r="P7" t="n">
-        <v>335.8926559075503</v>
+        <v>335.9148673158357</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -24565,28 +24623,28 @@
         <v>0.1041</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1775443815879351</v>
+        <v>0.1756477009260566</v>
       </c>
       <c r="J8" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K8" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05063889263099264</v>
+        <v>0.04979424096123153</v>
       </c>
       <c r="M8" t="n">
-        <v>4.332229893217741</v>
+        <v>4.327616008946145</v>
       </c>
       <c r="N8" t="n">
-        <v>34.76241895466543</v>
+        <v>34.71789921146279</v>
       </c>
       <c r="O8" t="n">
-        <v>5.895966329166528</v>
+        <v>5.892189678842899</v>
       </c>
       <c r="P8" t="n">
-        <v>333.2646386995145</v>
+        <v>333.2835847933918</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -24643,28 +24701,28 @@
         <v>0.0634</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2735629093114932</v>
+        <v>0.2717137772962915</v>
       </c>
       <c r="J9" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K9" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08414778637211195</v>
+        <v>0.08342503568040016</v>
       </c>
       <c r="M9" t="n">
-        <v>4.998419203548478</v>
+        <v>4.994536312146912</v>
       </c>
       <c r="N9" t="n">
-        <v>47.91218947278556</v>
+        <v>47.83269674356269</v>
       </c>
       <c r="O9" t="n">
-        <v>6.921863150394231</v>
+        <v>6.916118618384353</v>
       </c>
       <c r="P9" t="n">
-        <v>329.5352718283124</v>
+        <v>329.5537429549792</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -24721,28 +24779,28 @@
         <v>0.07539999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2770645581515733</v>
+        <v>0.2762833584367874</v>
       </c>
       <c r="J10" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K10" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L10" t="n">
-        <v>0.08243939437070702</v>
+        <v>0.08237904271418695</v>
       </c>
       <c r="M10" t="n">
-        <v>5.16982873092052</v>
+        <v>5.160238501175301</v>
       </c>
       <c r="N10" t="n">
-        <v>50.25864812245782</v>
+        <v>50.14019203823696</v>
       </c>
       <c r="O10" t="n">
-        <v>7.089333404662093</v>
+        <v>7.080973947010182</v>
       </c>
       <c r="P10" t="n">
-        <v>333.3316418948028</v>
+        <v>333.3394453608426</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -24799,28 +24857,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1550669711324817</v>
+        <v>0.153512140258218</v>
       </c>
       <c r="J11" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K11" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03278803681155062</v>
+        <v>0.0322891962981684</v>
       </c>
       <c r="M11" t="n">
-        <v>4.9280870788315</v>
+        <v>4.922789245294348</v>
       </c>
       <c r="N11" t="n">
-        <v>41.72474968583717</v>
+        <v>41.64892197247792</v>
       </c>
       <c r="O11" t="n">
-        <v>6.459469768164967</v>
+        <v>6.453597599206037</v>
       </c>
       <c r="P11" t="n">
-        <v>330.1650693246086</v>
+        <v>330.1806006537875</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -24877,28 +24935,28 @@
         <v>0.073</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.03417072111981874</v>
+        <v>-0.03739358648751492</v>
       </c>
       <c r="J12" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K12" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L12" t="n">
-        <v>0.001072701018597577</v>
+        <v>0.001288269760239324</v>
       </c>
       <c r="M12" t="n">
-        <v>6.138544906083204</v>
+        <v>6.135703855768541</v>
       </c>
       <c r="N12" t="n">
-        <v>63.96057555112888</v>
+        <v>63.92305721096736</v>
       </c>
       <c r="O12" t="n">
-        <v>7.997535592363993</v>
+        <v>7.995189629456412</v>
       </c>
       <c r="P12" t="n">
-        <v>331.8975760715516</v>
+        <v>331.9297695298588</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -24955,28 +25013,28 @@
         <v>0.0456</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.06240873629305275</v>
+        <v>-0.06307797583018068</v>
       </c>
       <c r="J13" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K13" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L13" t="n">
-        <v>0.002353375342855957</v>
+        <v>0.002415868125881016</v>
       </c>
       <c r="M13" t="n">
-        <v>7.831048267727981</v>
+        <v>7.815059995884185</v>
       </c>
       <c r="N13" t="n">
-        <v>97.12369631305607</v>
+        <v>96.886164232716</v>
       </c>
       <c r="O13" t="n">
-        <v>9.855135529918199</v>
+        <v>9.843076969764892</v>
       </c>
       <c r="P13" t="n">
-        <v>330.6864480962853</v>
+        <v>330.6931331832121</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -25014,7 +25072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N400"/>
+  <dimension ref="A1:N401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53817,6 +53875,78 @@
         </is>
       </c>
     </row>
+    <row r="401">
+      <c r="A401" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-15 22:01:19+00:00</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>-41.18989764001017,175.99242033763622</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>-41.19052876800584,175.99207720880216</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>-41.19116931803251,175.99178217317146</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>-41.191816360721106,175.991465425766</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>-41.19250590403143,175.99138400415413</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>-41.19319205278993,175.99129938818845</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>-41.193877054600655,175.99126279727287</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>-41.19455594504302,175.9912495158967</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>-41.195240414446175,175.9913233261039</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>-41.195929817984,175.9913965487012</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>-41.19660885382952,175.99149444048516</t>
+        </is>
+      </c>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>-41.197263393175355,175.9917265555257</t>
+        </is>
+      </c>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0346/nzd0346.xlsx
+++ b/data/nzd0346/nzd0346.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N401"/>
+  <dimension ref="A1:N404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19700,6 +19700,150 @@
       <c r="N401" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-09 22:01:21+00:00</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>339.12</v>
+      </c>
+      <c r="C402" t="n">
+        <v>330.58</v>
+      </c>
+      <c r="D402" t="n">
+        <v>326.02</v>
+      </c>
+      <c r="E402" t="n">
+        <v>321.05</v>
+      </c>
+      <c r="F402" t="n">
+        <v>330.45</v>
+      </c>
+      <c r="G402" t="n">
+        <v>333.91</v>
+      </c>
+      <c r="H402" t="n">
+        <v>332.36</v>
+      </c>
+      <c r="I402" t="n">
+        <v>332.98</v>
+      </c>
+      <c r="J402" t="n">
+        <v>339.09</v>
+      </c>
+      <c r="K402" t="n">
+        <v>327.78</v>
+      </c>
+      <c r="L402" t="n">
+        <v>322.95</v>
+      </c>
+      <c r="M402" t="n">
+        <v>323.43</v>
+      </c>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-17 22:01:18+00:00</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>339.14</v>
+      </c>
+      <c r="C403" t="n">
+        <v>329.02</v>
+      </c>
+      <c r="D403" t="n">
+        <v>324.85</v>
+      </c>
+      <c r="E403" t="n">
+        <v>319.87</v>
+      </c>
+      <c r="F403" t="n">
+        <v>330.59</v>
+      </c>
+      <c r="G403" t="n">
+        <v>334.38</v>
+      </c>
+      <c r="H403" t="n">
+        <v>332.86</v>
+      </c>
+      <c r="I403" t="n">
+        <v>333.3</v>
+      </c>
+      <c r="J403" t="n">
+        <v>339.47</v>
+      </c>
+      <c r="K403" t="n">
+        <v>329.08</v>
+      </c>
+      <c r="L403" t="n">
+        <v>323.26</v>
+      </c>
+      <c r="M403" t="n">
+        <v>322.39</v>
+      </c>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-18 21:55:15+00:00</t>
+        </is>
+      </c>
+      <c r="B404" t="n">
+        <v>339.14</v>
+      </c>
+      <c r="C404" t="n">
+        <v>329.02</v>
+      </c>
+      <c r="D404" t="n">
+        <v>324.85</v>
+      </c>
+      <c r="E404" t="n">
+        <v>319.87</v>
+      </c>
+      <c r="F404" t="n">
+        <v>330.59</v>
+      </c>
+      <c r="G404" t="n">
+        <v>334.98</v>
+      </c>
+      <c r="H404" t="n">
+        <v>333.82</v>
+      </c>
+      <c r="I404" t="n">
+        <v>334.43</v>
+      </c>
+      <c r="J404" t="n">
+        <v>341.42</v>
+      </c>
+      <c r="K404" t="n">
+        <v>331.09</v>
+      </c>
+      <c r="L404" t="n">
+        <v>324.39</v>
+      </c>
+      <c r="M404" t="n">
+        <v>322.44</v>
+      </c>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -19714,7 +19858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B427"/>
+  <dimension ref="A1:B430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23987,6 +24131,36 @@
       </c>
       <c r="B427" t="n">
         <v>-0.23</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2025-12-09 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B428" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2025-12-17 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2025-12-18 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -24155,28 +24329,28 @@
         <v>0.1454</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1717048418150572</v>
+        <v>-0.1730511201569848</v>
       </c>
       <c r="J2" t="n">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="K2" t="n">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07244088026262641</v>
+        <v>0.07449638622500032</v>
       </c>
       <c r="M2" t="n">
-        <v>3.685987808569938</v>
+        <v>3.665314983890929</v>
       </c>
       <c r="N2" t="n">
-        <v>22.26142297101676</v>
+        <v>22.10287865275485</v>
       </c>
       <c r="O2" t="n">
-        <v>4.718201243166378</v>
+        <v>4.701369869809739</v>
       </c>
       <c r="P2" t="n">
-        <v>344.6487503018628</v>
+        <v>344.662252894933</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24233,28 +24407,28 @@
         <v>0.1252</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1256765823733336</v>
+        <v>-0.1318122917234079</v>
       </c>
       <c r="J3" t="n">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="K3" t="n">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03808112902574479</v>
+        <v>0.04206751600194947</v>
       </c>
       <c r="M3" t="n">
-        <v>3.592463939356928</v>
+        <v>3.591312876695877</v>
       </c>
       <c r="N3" t="n">
-        <v>23.52704104854575</v>
+        <v>23.50482112707329</v>
       </c>
       <c r="O3" t="n">
-        <v>4.850468126742588</v>
+        <v>4.848177093204547</v>
       </c>
       <c r="P3" t="n">
-        <v>337.3742467341596</v>
+        <v>337.4357912985735</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24311,28 +24485,28 @@
         <v>0.1507</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03962233068766199</v>
+        <v>-0.04907482442235646</v>
       </c>
       <c r="J4" t="n">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="K4" t="n">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003475636153641326</v>
+        <v>0.005329794580194225</v>
       </c>
       <c r="M4" t="n">
-        <v>3.739372167429895</v>
+        <v>3.741121142305875</v>
       </c>
       <c r="N4" t="n">
-        <v>26.54383130918833</v>
+        <v>26.70196633518707</v>
       </c>
       <c r="O4" t="n">
-        <v>5.152070584647334</v>
+        <v>5.167394540306272</v>
       </c>
       <c r="P4" t="n">
-        <v>333.2528935106985</v>
+        <v>333.3477028782233</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -24389,28 +24563,28 @@
         <v>0.077</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.03569157998276765</v>
+        <v>-0.0536465204621658</v>
       </c>
       <c r="J5" t="n">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="K5" t="n">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002855343890456274</v>
+        <v>0.006220259007336915</v>
       </c>
       <c r="M5" t="n">
-        <v>3.898407186787031</v>
+        <v>3.950205822547075</v>
       </c>
       <c r="N5" t="n">
-        <v>26.23380278078323</v>
+        <v>27.316300671864</v>
       </c>
       <c r="O5" t="n">
-        <v>5.121894452327501</v>
+        <v>5.226499849025541</v>
       </c>
       <c r="P5" t="n">
-        <v>334.443927143011</v>
+        <v>334.6240131309096</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24467,28 +24641,28 @@
         <v>0.116</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05985923065936146</v>
+        <v>0.05395374586283744</v>
       </c>
       <c r="J6" t="n">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="K6" t="n">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00905313532280505</v>
+        <v>0.007432898107976538</v>
       </c>
       <c r="M6" t="n">
-        <v>3.778429980677466</v>
+        <v>3.780308110645001</v>
       </c>
       <c r="N6" t="n">
-        <v>23.12829267526723</v>
+        <v>23.09415082921828</v>
       </c>
       <c r="O6" t="n">
-        <v>4.809188359304222</v>
+        <v>4.805637400930108</v>
       </c>
       <c r="P6" t="n">
-        <v>333.3222906368453</v>
+        <v>333.3815201118736</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24545,28 +24719,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1122886290746248</v>
+        <v>0.106250732562282</v>
       </c>
       <c r="J7" t="n">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="K7" t="n">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02815381173786724</v>
+        <v>0.02550966862158499</v>
       </c>
       <c r="M7" t="n">
-        <v>3.778731296773701</v>
+        <v>3.783938383284155</v>
       </c>
       <c r="N7" t="n">
-        <v>25.6662162863294</v>
+        <v>25.62085864251566</v>
       </c>
       <c r="O7" t="n">
-        <v>5.066183601719287</v>
+        <v>5.061705112164839</v>
       </c>
       <c r="P7" t="n">
-        <v>335.9148673158357</v>
+        <v>335.9754223971063</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -24623,28 +24797,28 @@
         <v>0.1041</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1756477009260566</v>
+        <v>0.1690059520144329</v>
       </c>
       <c r="J8" t="n">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="K8" t="n">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04979424096123153</v>
+        <v>0.04670375422320394</v>
       </c>
       <c r="M8" t="n">
-        <v>4.327616008946145</v>
+        <v>4.317539097379475</v>
       </c>
       <c r="N8" t="n">
-        <v>34.71789921146279</v>
+        <v>34.63675413403889</v>
       </c>
       <c r="O8" t="n">
-        <v>5.892189678842899</v>
+        <v>5.885299833826556</v>
       </c>
       <c r="P8" t="n">
-        <v>333.2835847933918</v>
+        <v>333.3501954485351</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -24701,28 +24875,28 @@
         <v>0.0634</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2717137772962915</v>
+        <v>0.2674510634492832</v>
       </c>
       <c r="J9" t="n">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="K9" t="n">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08342503568040016</v>
+        <v>0.08203660598070239</v>
       </c>
       <c r="M9" t="n">
-        <v>4.994536312146912</v>
+        <v>4.976936931107403</v>
       </c>
       <c r="N9" t="n">
-        <v>47.83269674356269</v>
+        <v>47.55141375717305</v>
       </c>
       <c r="O9" t="n">
-        <v>6.916118618384353</v>
+        <v>6.895753313248165</v>
       </c>
       <c r="P9" t="n">
-        <v>329.5537429549792</v>
+        <v>329.5964930069922</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -24779,28 +24953,28 @@
         <v>0.07539999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2762833584367874</v>
+        <v>0.275439751236331</v>
       </c>
       <c r="J10" t="n">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="L10" t="n">
-        <v>0.08237904271418695</v>
+        <v>0.08302954383880301</v>
       </c>
       <c r="M10" t="n">
-        <v>5.160238501175301</v>
+        <v>5.129418784255571</v>
       </c>
       <c r="N10" t="n">
-        <v>50.14019203823696</v>
+        <v>49.77749336324401</v>
       </c>
       <c r="O10" t="n">
-        <v>7.080973947010182</v>
+        <v>7.055316673491276</v>
       </c>
       <c r="P10" t="n">
-        <v>333.3394453608426</v>
+        <v>333.3479010231868</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -24857,28 +25031,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.153512140258218</v>
+        <v>0.1468525309905027</v>
       </c>
       <c r="J11" t="n">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="K11" t="n">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0322891962981684</v>
+        <v>0.02992818554374754</v>
       </c>
       <c r="M11" t="n">
-        <v>4.922789245294348</v>
+        <v>4.916098278499885</v>
       </c>
       <c r="N11" t="n">
-        <v>41.64892197247792</v>
+        <v>41.52823440967241</v>
       </c>
       <c r="O11" t="n">
-        <v>6.453597599206037</v>
+        <v>6.444240405949518</v>
       </c>
       <c r="P11" t="n">
-        <v>330.1806006537875</v>
+        <v>330.2473853978747</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -24935,28 +25109,28 @@
         <v>0.073</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.03739358648751492</v>
+        <v>-0.04744339557084419</v>
       </c>
       <c r="J12" t="n">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="K12" t="n">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="L12" t="n">
-        <v>0.001288269760239324</v>
+        <v>0.002089974011903251</v>
       </c>
       <c r="M12" t="n">
-        <v>6.135703855768541</v>
+        <v>6.128578996036556</v>
       </c>
       <c r="N12" t="n">
-        <v>63.92305721096736</v>
+        <v>63.84973889636073</v>
       </c>
       <c r="O12" t="n">
-        <v>7.995189629456412</v>
+        <v>7.99060316223755</v>
       </c>
       <c r="P12" t="n">
-        <v>331.9297695298588</v>
+        <v>332.0305621427576</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -25013,28 +25187,28 @@
         <v>0.0456</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.06307797583018068</v>
+        <v>-0.07159463819124703</v>
       </c>
       <c r="J13" t="n">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="K13" t="n">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="L13" t="n">
-        <v>0.002415868125881016</v>
+        <v>0.003147246494440425</v>
       </c>
       <c r="M13" t="n">
-        <v>7.815059995884185</v>
+        <v>7.801891769596603</v>
       </c>
       <c r="N13" t="n">
-        <v>96.886164232716</v>
+        <v>96.45357928631128</v>
       </c>
       <c r="O13" t="n">
-        <v>9.843076969764892</v>
+        <v>9.82107831586284</v>
       </c>
       <c r="P13" t="n">
-        <v>330.6931331832121</v>
+        <v>330.7785559184993</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -25072,7 +25246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N401"/>
+  <dimension ref="A1:N404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53947,6 +54121,222 @@
         </is>
       </c>
     </row>
+    <row r="402">
+      <c r="A402" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-09 22:01:21+00:00</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>-41.189895559836,175.9924097269377</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>-41.19052646170196,175.99206544465972</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>-41.191166355990525,175.99176706418038</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>-41.1918154807392,175.99146006972646</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>-41.19250655509121,175.99138977898886</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>-41.193191967825655,175.99129772373837</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>-41.19387711981091,175.99124575736823</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>-41.19455588528476,175.9912529707161</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>-41.195240227367734,175.99132545671176</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>-41.19593570990874,175.9913608061963</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>-41.19661095246294,175.99148248492827</t>
+        </is>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>-41.19727213462369,175.9916783515398</t>
+        </is>
+      </c>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-17 22:01:18+00:00</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>-41.18989560505719,175.99240995760505</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>-41.19052293441131,175.9920474524433</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>-41.19116371050092,175.9917535698917</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>-41.191813223393126,175.9914463303212</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>-41.192506741108225,175.99139142894168</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>-41.19319225306274,175.99130331153498</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>-41.193877097010414,175.99125171537688</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>-41.19455581934449,175.99125678293058</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>-41.19523983242422,175.99132995466172</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>-41.195933214958224,175.9913759414598</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>-41.19661032083554,175.99148608320277</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>-41.19727431998268,175.99166630054117</t>
+        </is>
+      </c>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-18 21:55:15+00:00</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>-41.18989560505719,175.99240995760505</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>-41.19052293441131,175.9920474524433</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>-41.19116371050092,175.9917535698917</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>-41.191813223393126,175.9914463303212</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>-41.192506741108225,175.99139142894168</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>-41.19319261719478,175.99131044489235</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>-41.1938770532326,175.9912631547534</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>-41.19455558649189,175.99127024481288</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>-41.19523780573768,175.99135303624593</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>-41.195929357377054,175.99139934290324</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>-41.19660801845084,175.99149919949298</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>-41.197274214917364,175.99166687991612</t>
+        </is>
+      </c>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0346/nzd0346.xlsx
+++ b/data/nzd0346/nzd0346.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N404"/>
+  <dimension ref="A1:N405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19842,6 +19842,54 @@
         <v>322.44</v>
       </c>
       <c r="N404" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-27 22:01:11+00:00</t>
+        </is>
+      </c>
+      <c r="B405" t="n">
+        <v>341.44</v>
+      </c>
+      <c r="C405" t="n">
+        <v>330.08</v>
+      </c>
+      <c r="D405" t="n">
+        <v>326.76</v>
+      </c>
+      <c r="E405" t="n">
+        <v>326.98</v>
+      </c>
+      <c r="F405" t="n">
+        <v>331.23</v>
+      </c>
+      <c r="G405" t="n">
+        <v>336.2</v>
+      </c>
+      <c r="H405" t="n">
+        <v>336.51</v>
+      </c>
+      <c r="I405" t="n">
+        <v>338.28</v>
+      </c>
+      <c r="J405" t="n">
+        <v>345.23</v>
+      </c>
+      <c r="K405" t="n">
+        <v>337.58</v>
+      </c>
+      <c r="L405" t="n">
+        <v>326.07</v>
+      </c>
+      <c r="M405" t="n">
+        <v>320.75</v>
+      </c>
+      <c r="N405" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -19858,7 +19906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B430"/>
+  <dimension ref="A1:B431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24161,6 +24209,16 @@
       </c>
       <c r="B430" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-02-27 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>-0.43</v>
       </c>
     </row>
   </sheetData>
@@ -24329,28 +24387,28 @@
         <v>0.1454</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1730511201569848</v>
+        <v>-0.1724234237728322</v>
       </c>
       <c r="J2" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K2" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07449638622500032</v>
+        <v>0.07432948356735625</v>
       </c>
       <c r="M2" t="n">
-        <v>3.665314983890929</v>
+        <v>3.659898005765205</v>
       </c>
       <c r="N2" t="n">
-        <v>22.10287865275485</v>
+        <v>22.0527998732564</v>
       </c>
       <c r="O2" t="n">
-        <v>4.701369869809739</v>
+        <v>4.696040872187592</v>
       </c>
       <c r="P2" t="n">
-        <v>344.662252894933</v>
+        <v>344.6558937444474</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24407,28 +24465,28 @@
         <v>0.1252</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1318122917234079</v>
+        <v>-0.1335754208968348</v>
       </c>
       <c r="J3" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K3" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04206751600194947</v>
+        <v>0.04329617912298267</v>
       </c>
       <c r="M3" t="n">
-        <v>3.591312876695877</v>
+        <v>3.589741065062375</v>
       </c>
       <c r="N3" t="n">
-        <v>23.50482112707329</v>
+        <v>23.48318128879092</v>
       </c>
       <c r="O3" t="n">
-        <v>4.848177093204547</v>
+        <v>4.845944829317697</v>
       </c>
       <c r="P3" t="n">
-        <v>337.4357912985735</v>
+        <v>337.4536534434295</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24485,28 +24543,28 @@
         <v>0.1507</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04907482442235646</v>
+        <v>-0.05148894964833624</v>
       </c>
       <c r="J4" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K4" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005329794580194225</v>
+        <v>0.005878425151166988</v>
       </c>
       <c r="M4" t="n">
-        <v>3.741121142305875</v>
+        <v>3.739861944153059</v>
       </c>
       <c r="N4" t="n">
-        <v>26.70196633518707</v>
+        <v>26.70437775264105</v>
       </c>
       <c r="O4" t="n">
-        <v>5.167394540306272</v>
+        <v>5.16762786514674</v>
       </c>
       <c r="P4" t="n">
-        <v>333.3477028782233</v>
+        <v>333.3721602209619</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -24563,28 +24621,28 @@
         <v>0.077</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0536465204621658</v>
+        <v>-0.05649002902807979</v>
       </c>
       <c r="J5" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K5" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006220259007336915</v>
+        <v>0.006903245650936474</v>
       </c>
       <c r="M5" t="n">
-        <v>3.950205822547075</v>
+        <v>3.953350019580315</v>
       </c>
       <c r="N5" t="n">
-        <v>27.316300671864</v>
+        <v>27.34372778003902</v>
       </c>
       <c r="O5" t="n">
-        <v>5.226499849025541</v>
+        <v>5.229123041202896</v>
       </c>
       <c r="P5" t="n">
-        <v>334.6240131309096</v>
+        <v>334.6528205278202</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24641,28 +24699,28 @@
         <v>0.116</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05395374586283744</v>
+        <v>0.05231602431939152</v>
       </c>
       <c r="J6" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K6" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007432898107976538</v>
+        <v>0.007017257819604383</v>
       </c>
       <c r="M6" t="n">
-        <v>3.780308110645001</v>
+        <v>3.779264065126631</v>
       </c>
       <c r="N6" t="n">
-        <v>23.09415082921828</v>
+        <v>23.06851428223652</v>
       </c>
       <c r="O6" t="n">
-        <v>4.805637400930108</v>
+        <v>4.80296931931035</v>
       </c>
       <c r="P6" t="n">
-        <v>333.3815201118736</v>
+        <v>333.3981117603378</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24719,28 +24777,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.106250732562282</v>
+        <v>0.1050639486798895</v>
       </c>
       <c r="J7" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K7" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02550966862158499</v>
+        <v>0.02506458826979341</v>
       </c>
       <c r="M7" t="n">
-        <v>3.783938383284155</v>
+        <v>3.781008730273766</v>
       </c>
       <c r="N7" t="n">
-        <v>25.62085864251566</v>
+        <v>25.57399641020073</v>
       </c>
       <c r="O7" t="n">
-        <v>5.061705112164839</v>
+        <v>5.057073898036367</v>
       </c>
       <c r="P7" t="n">
-        <v>335.9754223971063</v>
+        <v>335.9874456259993</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -24797,28 +24855,28 @@
         <v>0.1041</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1690059520144329</v>
+        <v>0.1683994515671255</v>
       </c>
       <c r="J8" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K8" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04670375422320394</v>
+        <v>0.04660319745036856</v>
       </c>
       <c r="M8" t="n">
-        <v>4.317539097379475</v>
+        <v>4.30886130036779</v>
       </c>
       <c r="N8" t="n">
-        <v>34.63675413403889</v>
+        <v>34.55534341233245</v>
       </c>
       <c r="O8" t="n">
-        <v>5.885299833826556</v>
+        <v>5.878379318513943</v>
       </c>
       <c r="P8" t="n">
-        <v>333.3501954485351</v>
+        <v>333.3563398643887</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -24875,28 +24933,28 @@
         <v>0.0634</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2674510634492832</v>
+        <v>0.2681767854905683</v>
       </c>
       <c r="J9" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K9" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08203660598070239</v>
+        <v>0.08281891737073754</v>
       </c>
       <c r="M9" t="n">
-        <v>4.976936931107403</v>
+        <v>4.969160326738796</v>
       </c>
       <c r="N9" t="n">
-        <v>47.55141375717305</v>
+        <v>47.43990302414768</v>
       </c>
       <c r="O9" t="n">
-        <v>6.895753313248165</v>
+        <v>6.887663103270055</v>
       </c>
       <c r="P9" t="n">
-        <v>329.5964930069922</v>
+        <v>329.5891407650681</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -24953,28 +25011,28 @@
         <v>0.07539999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>0.275439751236331</v>
+        <v>0.2775273720259736</v>
       </c>
       <c r="J10" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K10" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L10" t="n">
-        <v>0.08302954383880301</v>
+        <v>0.08449726482238784</v>
       </c>
       <c r="M10" t="n">
-        <v>5.129418784255571</v>
+        <v>5.130443121862574</v>
       </c>
       <c r="N10" t="n">
-        <v>49.77749336324401</v>
+        <v>49.70550986427293</v>
       </c>
       <c r="O10" t="n">
-        <v>7.055316673491276</v>
+        <v>7.050213462319629</v>
       </c>
       <c r="P10" t="n">
-        <v>333.3479010231868</v>
+        <v>333.3267514752632</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -25031,28 +25089,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1468525309905027</v>
+        <v>0.148420251392212</v>
       </c>
       <c r="J11" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K11" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02992818554374754</v>
+        <v>0.03068028215154583</v>
       </c>
       <c r="M11" t="n">
-        <v>4.916098278499885</v>
+        <v>4.913777393891669</v>
       </c>
       <c r="N11" t="n">
-        <v>41.52823440967241</v>
+        <v>41.45433140802864</v>
       </c>
       <c r="O11" t="n">
-        <v>6.444240405949518</v>
+        <v>6.438503817505169</v>
       </c>
       <c r="P11" t="n">
-        <v>330.2473853978747</v>
+        <v>330.2315029263399</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -25109,28 +25167,28 @@
         <v>0.073</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.04744339557084419</v>
+        <v>-0.04959257348852909</v>
       </c>
       <c r="J12" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K12" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L12" t="n">
-        <v>0.002089974011903251</v>
+        <v>0.002292764467679009</v>
       </c>
       <c r="M12" t="n">
-        <v>6.128578996036556</v>
+        <v>6.121555985160967</v>
       </c>
       <c r="N12" t="n">
-        <v>63.84973889636073</v>
+        <v>63.74598874790337</v>
       </c>
       <c r="O12" t="n">
-        <v>7.99060316223755</v>
+        <v>7.984108513034086</v>
       </c>
       <c r="P12" t="n">
-        <v>332.0305621427576</v>
+        <v>332.0523353218674</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -25187,28 +25245,28 @@
         <v>0.0456</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.07159463819124703</v>
+        <v>-0.07530980098056231</v>
       </c>
       <c r="J13" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K13" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L13" t="n">
-        <v>0.003147246494440425</v>
+        <v>0.003492895189824985</v>
       </c>
       <c r="M13" t="n">
-        <v>7.801891769596603</v>
+        <v>7.801812792522965</v>
       </c>
       <c r="N13" t="n">
-        <v>96.45357928631128</v>
+        <v>96.37707389973416</v>
       </c>
       <c r="O13" t="n">
-        <v>9.82107831586284</v>
+        <v>9.817182584618367</v>
       </c>
       <c r="P13" t="n">
-        <v>330.7785559184993</v>
+        <v>330.8161939866036</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -25246,7 +25304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N404"/>
+  <dimension ref="A1:N405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54337,6 +54395,78 @@
         </is>
       </c>
     </row>
+    <row r="405">
+      <c r="A405" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-27 22:01:11+00:00</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>-41.18990080549065,175.9924364843526</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>-41.190525331160394,175.9920596779235</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>-41.19116802920533,175.99177559903015</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>-41.19182682483432,175.99152911607246</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>-41.192507591471454,175.99139897158315</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>-41.19319335759524,175.99132494938584</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>-41.193876930557416,175.99129520883923</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>-41.194554793132724,175.9913161105167</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>-41.19523384589076,175.9913981341056</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>-41.19591690177212,175.99147490276707</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>-41.19660459543371,175.99151869981645</t>
+        </is>
+      </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>-41.19727776612319,175.99164729704148</t>
+        </is>
+      </c>
+      <c r="N405" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0346/nzd0346.xlsx
+++ b/data/nzd0346/nzd0346.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N405"/>
+  <dimension ref="A1:N407"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19890,6 +19890,102 @@
         <v>320.75</v>
       </c>
       <c r="N405" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-07 22:00:56+00:00</t>
+        </is>
+      </c>
+      <c r="B406" t="n">
+        <v>340.68</v>
+      </c>
+      <c r="C406" t="n">
+        <v>329.65</v>
+      </c>
+      <c r="D406" t="n">
+        <v>326.5</v>
+      </c>
+      <c r="E406" t="n">
+        <v>326.66</v>
+      </c>
+      <c r="F406" t="n">
+        <v>331.21</v>
+      </c>
+      <c r="G406" t="n">
+        <v>335.4</v>
+      </c>
+      <c r="H406" t="n">
+        <v>336.25</v>
+      </c>
+      <c r="I406" t="n">
+        <v>337.53</v>
+      </c>
+      <c r="J406" t="n">
+        <v>344.79</v>
+      </c>
+      <c r="K406" t="n">
+        <v>337.26</v>
+      </c>
+      <c r="L406" t="n">
+        <v>327.98</v>
+      </c>
+      <c r="M406" t="n">
+        <v>322.76</v>
+      </c>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-15 22:00:37+00:00</t>
+        </is>
+      </c>
+      <c r="B407" t="n">
+        <v>339.69</v>
+      </c>
+      <c r="C407" t="n">
+        <v>329.16</v>
+      </c>
+      <c r="D407" t="n">
+        <v>326.43</v>
+      </c>
+      <c r="E407" t="n">
+        <v>326.2</v>
+      </c>
+      <c r="F407" t="n">
+        <v>330.97</v>
+      </c>
+      <c r="G407" t="n">
+        <v>335.7</v>
+      </c>
+      <c r="H407" t="n">
+        <v>335.82</v>
+      </c>
+      <c r="I407" t="n">
+        <v>336.74</v>
+      </c>
+      <c r="J407" t="n">
+        <v>344.4</v>
+      </c>
+      <c r="K407" t="n">
+        <v>337.22</v>
+      </c>
+      <c r="L407" t="n">
+        <v>328.64</v>
+      </c>
+      <c r="M407" t="n">
+        <v>324.62</v>
+      </c>
+      <c r="N407" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -19906,7 +20002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B431"/>
+  <dimension ref="A1:B433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24219,6 +24315,26 @@
       </c>
       <c r="B431" t="n">
         <v>-0.43</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-03-07 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B432" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-03-15 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -24387,28 +24503,28 @@
         <v>0.1454</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1724234237728322</v>
+        <v>-0.1723232846166196</v>
       </c>
       <c r="J2" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="K2" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07432948356735625</v>
+        <v>0.07493718942358807</v>
       </c>
       <c r="M2" t="n">
-        <v>3.659898005765205</v>
+        <v>3.64433588646622</v>
       </c>
       <c r="N2" t="n">
-        <v>22.0527998732564</v>
+        <v>21.94542034324295</v>
       </c>
       <c r="O2" t="n">
-        <v>4.696040872187592</v>
+        <v>4.684593935790267</v>
       </c>
       <c r="P2" t="n">
-        <v>344.6558937444474</v>
+        <v>344.6548800467213</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24465,28 +24581,28 @@
         <v>0.1252</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1335754208968348</v>
+        <v>-0.1376412667419724</v>
       </c>
       <c r="J3" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="K3" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04329617912298267</v>
+        <v>0.04610415477242935</v>
       </c>
       <c r="M3" t="n">
-        <v>3.589741065062375</v>
+        <v>3.588810400105595</v>
       </c>
       <c r="N3" t="n">
-        <v>23.48318128879092</v>
+        <v>23.46607037869952</v>
       </c>
       <c r="O3" t="n">
-        <v>4.845944829317697</v>
+        <v>4.844179020092003</v>
       </c>
       <c r="P3" t="n">
-        <v>337.4536534434295</v>
+        <v>337.4949110003598</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24543,28 +24659,28 @@
         <v>0.1507</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.05148894964833624</v>
+        <v>-0.0564915649767496</v>
       </c>
       <c r="J4" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="K4" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005878425151166988</v>
+        <v>0.007098920993681368</v>
       </c>
       <c r="M4" t="n">
-        <v>3.739861944153059</v>
+        <v>3.737938299379259</v>
       </c>
       <c r="N4" t="n">
-        <v>26.70437775264105</v>
+        <v>26.72163370590831</v>
       </c>
       <c r="O4" t="n">
-        <v>5.16762786514674</v>
+        <v>5.169297215861003</v>
       </c>
       <c r="P4" t="n">
-        <v>333.3721602209619</v>
+        <v>333.4229222236191</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -24621,28 +24737,28 @@
         <v>0.077</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05649002902807979</v>
+        <v>-0.06256486213585863</v>
       </c>
       <c r="J5" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="K5" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006903245650936474</v>
+        <v>0.008471170963170183</v>
       </c>
       <c r="M5" t="n">
-        <v>3.953350019580315</v>
+        <v>3.961318270382902</v>
       </c>
       <c r="N5" t="n">
-        <v>27.34372778003902</v>
+        <v>27.42868819980862</v>
       </c>
       <c r="O5" t="n">
-        <v>5.229123041202896</v>
+        <v>5.237240513840148</v>
       </c>
       <c r="P5" t="n">
-        <v>334.6528205278202</v>
+        <v>334.7144633117082</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24699,28 +24815,28 @@
         <v>0.116</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05231602431939152</v>
+        <v>0.04897567479932004</v>
       </c>
       <c r="J6" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="K6" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007017257819604383</v>
+        <v>0.006198874402039478</v>
       </c>
       <c r="M6" t="n">
-        <v>3.779264065126631</v>
+        <v>3.777674453278392</v>
       </c>
       <c r="N6" t="n">
-        <v>23.06851428223652</v>
+        <v>23.02129016274063</v>
       </c>
       <c r="O6" t="n">
-        <v>4.80296931931035</v>
+        <v>4.79805066279428</v>
       </c>
       <c r="P6" t="n">
-        <v>333.3981117603378</v>
+        <v>333.4320070827104</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24777,28 +24893,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1050639486798895</v>
+        <v>0.1021436529936922</v>
       </c>
       <c r="J7" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="K7" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02506458826979341</v>
+        <v>0.02390972401042146</v>
       </c>
       <c r="M7" t="n">
-        <v>3.781008730273766</v>
+        <v>3.778102424635582</v>
       </c>
       <c r="N7" t="n">
-        <v>25.57399641020073</v>
+        <v>25.49883559466949</v>
       </c>
       <c r="O7" t="n">
-        <v>5.057073898036367</v>
+        <v>5.049637174557148</v>
       </c>
       <c r="P7" t="n">
-        <v>335.9874456259993</v>
+        <v>336.0170772991274</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -24855,28 +24971,28 @@
         <v>0.1041</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1683994515671255</v>
+        <v>0.1667783663535232</v>
       </c>
       <c r="J8" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="K8" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04660319745036856</v>
+        <v>0.04617020159049479</v>
       </c>
       <c r="M8" t="n">
-        <v>4.30886130036779</v>
+        <v>4.292961907119459</v>
       </c>
       <c r="N8" t="n">
-        <v>34.55534341233245</v>
+        <v>34.4009709595523</v>
       </c>
       <c r="O8" t="n">
-        <v>5.878379318513943</v>
+        <v>5.865234092476813</v>
       </c>
       <c r="P8" t="n">
-        <v>333.3563398643887</v>
+        <v>333.372790167234</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -24933,28 +25049,28 @@
         <v>0.0634</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2681767854905683</v>
+        <v>0.2685543956690358</v>
       </c>
       <c r="J9" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="K9" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08281891737073754</v>
+        <v>0.08379627563235215</v>
       </c>
       <c r="M9" t="n">
-        <v>4.969160326738796</v>
+        <v>4.947029223260592</v>
       </c>
       <c r="N9" t="n">
-        <v>47.43990302414768</v>
+        <v>47.20782820421379</v>
       </c>
       <c r="O9" t="n">
-        <v>6.887663103270055</v>
+        <v>6.870795310894787</v>
       </c>
       <c r="P9" t="n">
-        <v>329.5891407650681</v>
+        <v>329.5853110760565</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25011,28 +25127,28 @@
         <v>0.07539999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2775273720259736</v>
+        <v>0.281042434977309</v>
       </c>
       <c r="J10" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="K10" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L10" t="n">
-        <v>0.08449726482238784</v>
+        <v>0.08714115720973259</v>
       </c>
       <c r="M10" t="n">
-        <v>5.130443121862574</v>
+        <v>5.12810002746404</v>
       </c>
       <c r="N10" t="n">
-        <v>49.70550986427293</v>
+        <v>49.53432594046326</v>
       </c>
       <c r="O10" t="n">
-        <v>7.050213462319629</v>
+        <v>7.038062655337992</v>
       </c>
       <c r="P10" t="n">
-        <v>333.3267514752632</v>
+        <v>333.2910849245416</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -25089,28 +25205,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.148420251392212</v>
+        <v>0.1511873934635105</v>
       </c>
       <c r="J11" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="K11" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03068028215154583</v>
+        <v>0.03207385817824671</v>
       </c>
       <c r="M11" t="n">
-        <v>4.913777393891669</v>
+        <v>4.907022760821488</v>
       </c>
       <c r="N11" t="n">
-        <v>41.45433140802864</v>
+        <v>41.29565212561821</v>
       </c>
       <c r="O11" t="n">
-        <v>6.438503817505169</v>
+        <v>6.426169319712811</v>
       </c>
       <c r="P11" t="n">
-        <v>330.2315029263399</v>
+        <v>330.2034246699529</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -25167,28 +25283,28 @@
         <v>0.073</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.04959257348852909</v>
+        <v>-0.05178498501500085</v>
       </c>
       <c r="J12" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="K12" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L12" t="n">
-        <v>0.002292764467679009</v>
+        <v>0.002523393971620713</v>
       </c>
       <c r="M12" t="n">
-        <v>6.121555985160967</v>
+        <v>6.099885712521136</v>
       </c>
       <c r="N12" t="n">
-        <v>63.74598874790337</v>
+        <v>63.46108923291537</v>
       </c>
       <c r="O12" t="n">
-        <v>7.984108513034086</v>
+        <v>7.966246872456023</v>
       </c>
       <c r="P12" t="n">
-        <v>332.0523353218674</v>
+        <v>332.0745802271582</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -25245,28 +25361,28 @@
         <v>0.0456</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.07530980098056231</v>
+        <v>-0.07993648602943092</v>
       </c>
       <c r="J13" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="K13" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L13" t="n">
-        <v>0.003492895189824985</v>
+        <v>0.003967539297719425</v>
       </c>
       <c r="M13" t="n">
-        <v>7.801812792522965</v>
+        <v>7.78714809098583</v>
       </c>
       <c r="N13" t="n">
-        <v>96.37707389973416</v>
+        <v>96.03388881456164</v>
       </c>
       <c r="O13" t="n">
-        <v>9.817182584618367</v>
+        <v>9.799688199864404</v>
       </c>
       <c r="P13" t="n">
-        <v>330.8161939866036</v>
+        <v>330.8631366497115</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -25304,7 +25420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N405"/>
+  <dimension ref="A1:N407"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54467,6 +54583,150 @@
         </is>
       </c>
     </row>
+    <row r="406">
+      <c r="A406" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-07 22:00:56+00:00</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>-41.18989908708725,175.9924277189921</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>-41.19052435889441,175.99205471853048</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>-41.191167441319124,175.9917726002991</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>-41.191826212675124,175.99152539013082</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>-41.19250756489762,175.9913987358756</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>-41.19319287208696,175.99131543824254</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>-41.19387694241491,175.99129211067483</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>-41.19455494768465,175.99130717563952</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>-41.19523430319681,175.99139292595416</t>
+        </is>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>-41.19591751591711,175.9914711771659</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>-41.1966007037853,175.99154086982432</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>-41.19727354249933,175.99167058791576</t>
+        </is>
+      </c>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-15 22:00:37+00:00</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>-41.189896848639684,175.99241630095736</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>-41.19052325096315,175.99204906712933</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>-41.19116728304205,175.99177179294844</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>-41.19182533269607,175.9915200340898</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>-41.19250724601145,175.99139590738503</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>-41.19319305415266,175.99131900492128</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>-41.19387696202514,175.99128698678754</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>-41.19455511047859,175.99129776423544</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>-41.19523470853608,175.99138830963804</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>-41.19591759268522,175.99147071146572</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>-41.19659935902624,175.9915485306641</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>-41.19726963406717,175.99169214066222</t>
+        </is>
+      </c>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0346/nzd0346.xlsx
+++ b/data/nzd0346/nzd0346.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N407"/>
+  <dimension ref="A1:N409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19988,6 +19988,102 @@
       <c r="N407" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-23 22:00:23+00:00</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>338.8</v>
+      </c>
+      <c r="C408" t="n">
+        <v>328.64</v>
+      </c>
+      <c r="D408" t="n">
+        <v>326.25</v>
+      </c>
+      <c r="E408" t="n">
+        <v>326.26</v>
+      </c>
+      <c r="F408" t="n">
+        <v>330.53</v>
+      </c>
+      <c r="G408" t="n">
+        <v>334.96</v>
+      </c>
+      <c r="H408" t="n">
+        <v>335.88</v>
+      </c>
+      <c r="I408" t="n">
+        <v>336.42</v>
+      </c>
+      <c r="J408" t="n">
+        <v>343.96</v>
+      </c>
+      <c r="K408" t="n">
+        <v>337.22</v>
+      </c>
+      <c r="L408" t="n">
+        <v>328.64</v>
+      </c>
+      <c r="M408" t="n">
+        <v>324.62</v>
+      </c>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:00:14+00:00</t>
+        </is>
+      </c>
+      <c r="B409" t="n">
+        <v>336.24</v>
+      </c>
+      <c r="C409" t="n">
+        <v>326.59</v>
+      </c>
+      <c r="D409" t="n">
+        <v>325.06</v>
+      </c>
+      <c r="E409" t="n">
+        <v>325.05</v>
+      </c>
+      <c r="F409" t="n">
+        <v>328.95</v>
+      </c>
+      <c r="G409" t="n">
+        <v>334.32</v>
+      </c>
+      <c r="H409" t="n">
+        <v>334.74</v>
+      </c>
+      <c r="I409" t="n">
+        <v>336.62</v>
+      </c>
+      <c r="J409" t="n">
+        <v>343.57</v>
+      </c>
+      <c r="K409" t="n">
+        <v>336.51</v>
+      </c>
+      <c r="L409" t="n">
+        <v>328.93</v>
+      </c>
+      <c r="M409" t="n">
+        <v>324.61</v>
+      </c>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -20002,7 +20098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B433"/>
+  <dimension ref="A1:B435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24335,6 +24431,26 @@
       </c>
       <c r="B433" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-03-23 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>0.38</v>
       </c>
     </row>
   </sheetData>
@@ -24503,28 +24619,28 @@
         <v>0.1454</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1723232846166196</v>
+        <v>-0.1746042856115565</v>
       </c>
       <c r="J2" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K2" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07493718942358807</v>
+        <v>0.07735840274096362</v>
       </c>
       <c r="M2" t="n">
-        <v>3.64433588646622</v>
+        <v>3.637879848350363</v>
       </c>
       <c r="N2" t="n">
-        <v>21.94542034324295</v>
+        <v>21.87719130284822</v>
       </c>
       <c r="O2" t="n">
-        <v>4.684593935790267</v>
+        <v>4.677305987729286</v>
       </c>
       <c r="P2" t="n">
-        <v>344.6548800467213</v>
+        <v>344.6780997094846</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24581,28 +24697,28 @@
         <v>0.1252</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1376412667419724</v>
+        <v>-0.1432020057345972</v>
       </c>
       <c r="J3" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K3" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04610415477242935</v>
+        <v>0.0497983093221035</v>
       </c>
       <c r="M3" t="n">
-        <v>3.588810400105595</v>
+        <v>3.594154940853105</v>
       </c>
       <c r="N3" t="n">
-        <v>23.46607037869952</v>
+        <v>23.54266546726415</v>
       </c>
       <c r="O3" t="n">
-        <v>4.844179020092003</v>
+        <v>4.852078468786768</v>
       </c>
       <c r="P3" t="n">
-        <v>337.4949110003598</v>
+        <v>337.5514965951479</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24659,28 +24775,28 @@
         <v>0.1507</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0564915649767496</v>
+        <v>-0.06209343667718335</v>
       </c>
       <c r="J4" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K4" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007098920993681368</v>
+        <v>0.008587447413373028</v>
       </c>
       <c r="M4" t="n">
-        <v>3.737938299379259</v>
+        <v>3.73787390478101</v>
       </c>
       <c r="N4" t="n">
-        <v>26.72163370590831</v>
+        <v>26.78168803255307</v>
       </c>
       <c r="O4" t="n">
-        <v>5.169297215861003</v>
+        <v>5.175102707440025</v>
       </c>
       <c r="P4" t="n">
-        <v>333.4229222236191</v>
+        <v>333.4799221052928</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -24737,28 +24853,28 @@
         <v>0.077</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.06256486213585863</v>
+        <v>-0.06917922527923066</v>
       </c>
       <c r="J5" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K5" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L5" t="n">
-        <v>0.008471170963170183</v>
+        <v>0.0103398655839122</v>
       </c>
       <c r="M5" t="n">
-        <v>3.961318270382902</v>
+        <v>3.971861606004833</v>
       </c>
       <c r="N5" t="n">
-        <v>27.42868819980862</v>
+        <v>27.55997383793003</v>
       </c>
       <c r="O5" t="n">
-        <v>5.237240513840148</v>
+        <v>5.249759407623365</v>
       </c>
       <c r="P5" t="n">
-        <v>334.7144633117082</v>
+        <v>334.7817645028742</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24815,28 +24931,28 @@
         <v>0.116</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04897567479932004</v>
+        <v>0.04450323316027551</v>
       </c>
       <c r="J6" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K6" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006198874402039478</v>
+        <v>0.005147113980466522</v>
       </c>
       <c r="M6" t="n">
-        <v>3.777674453278392</v>
+        <v>3.78200805675207</v>
       </c>
       <c r="N6" t="n">
-        <v>23.02129016274063</v>
+        <v>23.03214760873387</v>
       </c>
       <c r="O6" t="n">
-        <v>4.79805066279428</v>
+        <v>4.799181972871405</v>
       </c>
       <c r="P6" t="n">
-        <v>333.4320070827104</v>
+        <v>333.4775179436943</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24893,28 +25009,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1021436529936922</v>
+        <v>0.09847871275977099</v>
       </c>
       <c r="J7" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K7" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02390972401042146</v>
+        <v>0.02240879477730096</v>
       </c>
       <c r="M7" t="n">
-        <v>3.778102424635582</v>
+        <v>3.779172675024669</v>
       </c>
       <c r="N7" t="n">
-        <v>25.49883559466949</v>
+        <v>25.45538924381301</v>
       </c>
       <c r="O7" t="n">
-        <v>5.049637174557148</v>
+        <v>5.04533341255194</v>
       </c>
       <c r="P7" t="n">
-        <v>336.0170772991274</v>
+        <v>336.0543679737746</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -24971,28 +25087,28 @@
         <v>0.1041</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1667783663535232</v>
+        <v>0.16453340723783</v>
       </c>
       <c r="J8" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K8" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04617020159049479</v>
+        <v>0.04537881060874105</v>
       </c>
       <c r="M8" t="n">
-        <v>4.292961907119459</v>
+        <v>4.279337562188522</v>
       </c>
       <c r="N8" t="n">
-        <v>34.4009709595523</v>
+        <v>34.26434020599295</v>
       </c>
       <c r="O8" t="n">
-        <v>5.865234092476813</v>
+        <v>5.853574993625088</v>
       </c>
       <c r="P8" t="n">
-        <v>333.372790167234</v>
+        <v>333.3956362462725</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25049,28 +25165,28 @@
         <v>0.0634</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2685543956690358</v>
+        <v>0.2683587936578869</v>
       </c>
       <c r="J9" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K9" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08379627563235215</v>
+        <v>0.08444783534863343</v>
       </c>
       <c r="M9" t="n">
-        <v>4.947029223260592</v>
+        <v>4.923688700834603</v>
       </c>
       <c r="N9" t="n">
-        <v>47.20782820421379</v>
+        <v>46.97669544721932</v>
       </c>
       <c r="O9" t="n">
-        <v>6.870795310894787</v>
+        <v>6.853954730461774</v>
       </c>
       <c r="P9" t="n">
-        <v>329.5853110760565</v>
+        <v>329.5873001973179</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25127,28 +25243,28 @@
         <v>0.07539999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>0.281042434977309</v>
+        <v>0.2837156929152319</v>
       </c>
       <c r="J10" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K10" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L10" t="n">
-        <v>0.08714115720973259</v>
+        <v>0.08939237004584166</v>
       </c>
       <c r="M10" t="n">
-        <v>5.12810002746404</v>
+        <v>5.120240453153913</v>
       </c>
       <c r="N10" t="n">
-        <v>49.53432594046326</v>
+        <v>49.33484623298256</v>
       </c>
       <c r="O10" t="n">
-        <v>7.038062655337992</v>
+        <v>7.023876866302722</v>
       </c>
       <c r="P10" t="n">
-        <v>333.2910849245416</v>
+        <v>333.263888843067</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -25205,28 +25321,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1511873934635105</v>
+        <v>0.1535460968043453</v>
       </c>
       <c r="J11" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K11" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03207385817824671</v>
+        <v>0.03334075514878609</v>
       </c>
       <c r="M11" t="n">
-        <v>4.907022760821488</v>
+        <v>4.897830808413708</v>
       </c>
       <c r="N11" t="n">
-        <v>41.29565212561821</v>
+        <v>41.12744857921319</v>
       </c>
       <c r="O11" t="n">
-        <v>6.426169319712811</v>
+        <v>6.413068577460652</v>
       </c>
       <c r="P11" t="n">
-        <v>330.2034246699529</v>
+        <v>330.1794304621557</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -25283,28 +25399,28 @@
         <v>0.073</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.05178498501500085</v>
+        <v>-0.05349367415261746</v>
       </c>
       <c r="J12" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K12" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L12" t="n">
-        <v>0.002523393971620713</v>
+        <v>0.002718213815988357</v>
       </c>
       <c r="M12" t="n">
-        <v>6.099885712521136</v>
+        <v>6.076591463068009</v>
       </c>
       <c r="N12" t="n">
-        <v>63.46108923291537</v>
+        <v>63.16774262443602</v>
       </c>
       <c r="O12" t="n">
-        <v>7.966246872456023</v>
+        <v>7.947813700913983</v>
       </c>
       <c r="P12" t="n">
-        <v>332.0745802271582</v>
+        <v>332.0919631526033</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -25361,28 +25477,28 @@
         <v>0.0456</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.07993648602943092</v>
+        <v>-0.08361988117822587</v>
       </c>
       <c r="J13" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K13" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L13" t="n">
-        <v>0.003967539297719425</v>
+        <v>0.004379322066651481</v>
       </c>
       <c r="M13" t="n">
-        <v>7.78714809098583</v>
+        <v>7.767942581961575</v>
       </c>
       <c r="N13" t="n">
-        <v>96.03388881456164</v>
+        <v>95.64501595096715</v>
       </c>
       <c r="O13" t="n">
-        <v>9.799688199864404</v>
+        <v>9.779826989827946</v>
       </c>
       <c r="P13" t="n">
-        <v>330.8631366497115</v>
+        <v>330.9006119577177</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -25420,7 +25536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N407"/>
+  <dimension ref="A1:N409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54727,6 +54843,150 @@
         </is>
       </c>
     </row>
+    <row r="408">
+      <c r="A408" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-23 22:00:23+00:00</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>-41.189894836296936,175.99240603626006</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>-41.19052207519905,175.9920430697242</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>-41.191166876043845,175.99176971690392</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>-41.19182544747595,175.99152073270383</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>-41.192506661386645,175.99139072181904</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>-41.193192605057064,175.99131020711377</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>-41.19387695928885,175.99128770174858</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>-41.1945551764202,175.99129395202112</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>-41.19523516584167,175.99138310148643</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>-41.19591759268522,175.99147071146572</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>-41.19659935902624,175.9915485306641</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>-41.19726963406717,175.99169214066222</t>
+        </is>
+      </c>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:00:14+00:00</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>-41.18988904797997,175.9923765108419</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>-41.19051743997205,175.99201942610978</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>-41.19116418533252,175.99175599194345</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>-41.19182313274729,175.99150664398783</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>-41.19250456205017,175.99137210092363</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>-41.19319221664951,175.99130259819924</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>-41.19387701127778,175.99127411748916</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>-41.19455513520672,175.99129633465506</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>-41.19523557118055,175.99137848517015</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>-41.19591895531897,175.99146244528782</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>-41.19659876814709,175.99155189679055</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>-41.197269655080255,175.99169202478723</t>
+        </is>
+      </c>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0346/nzd0346.xlsx
+++ b/data/nzd0346/nzd0346.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N409"/>
+  <dimension ref="A1:N412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20084,6 +20084,150 @@
       <c r="N409" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-24 22:00:36+00:00</t>
+        </is>
+      </c>
+      <c r="B410" t="n">
+        <v>335.16</v>
+      </c>
+      <c r="C410" t="n">
+        <v>326.3</v>
+      </c>
+      <c r="D410" t="n">
+        <v>324.61</v>
+      </c>
+      <c r="E410" t="n">
+        <v>325.33</v>
+      </c>
+      <c r="F410" t="n">
+        <v>328.74</v>
+      </c>
+      <c r="G410" t="n">
+        <v>334.07</v>
+      </c>
+      <c r="H410" t="n">
+        <v>335.34</v>
+      </c>
+      <c r="I410" t="n">
+        <v>337.51</v>
+      </c>
+      <c r="J410" t="n">
+        <v>344.09</v>
+      </c>
+      <c r="K410" t="n">
+        <v>336.53</v>
+      </c>
+      <c r="L410" t="n">
+        <v>329.97</v>
+      </c>
+      <c r="M410" t="n">
+        <v>324.61</v>
+      </c>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02 22:00:18+00:00</t>
+        </is>
+      </c>
+      <c r="B411" t="n">
+        <v>335.05</v>
+      </c>
+      <c r="C411" t="n">
+        <v>325.82</v>
+      </c>
+      <c r="D411" t="n">
+        <v>324.53</v>
+      </c>
+      <c r="E411" t="n">
+        <v>325</v>
+      </c>
+      <c r="F411" t="n">
+        <v>328.29</v>
+      </c>
+      <c r="G411" t="n">
+        <v>334.3</v>
+      </c>
+      <c r="H411" t="n">
+        <v>335.85</v>
+      </c>
+      <c r="I411" t="n">
+        <v>337.59</v>
+      </c>
+      <c r="J411" t="n">
+        <v>345.07</v>
+      </c>
+      <c r="K411" t="n">
+        <v>336.38</v>
+      </c>
+      <c r="L411" t="n">
+        <v>330.97</v>
+      </c>
+      <c r="M411" t="n">
+        <v>323.82</v>
+      </c>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:00:01+00:00</t>
+        </is>
+      </c>
+      <c r="B412" t="n">
+        <v>333.72</v>
+      </c>
+      <c r="C412" t="n">
+        <v>324.91</v>
+      </c>
+      <c r="D412" t="n">
+        <v>324.19</v>
+      </c>
+      <c r="E412" t="n">
+        <v>325.09</v>
+      </c>
+      <c r="F412" t="n">
+        <v>328.28</v>
+      </c>
+      <c r="G412" t="n">
+        <v>335.01</v>
+      </c>
+      <c r="H412" t="n">
+        <v>337.87</v>
+      </c>
+      <c r="I412" t="n">
+        <v>339.71</v>
+      </c>
+      <c r="J412" t="n">
+        <v>347.92</v>
+      </c>
+      <c r="K412" t="n">
+        <v>339.68</v>
+      </c>
+      <c r="L412" t="n">
+        <v>336.84</v>
+      </c>
+      <c r="M412" t="n">
+        <v>329.15</v>
+      </c>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -20098,7 +20242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B435"/>
+  <dimension ref="A1:B438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24451,6 +24595,36 @@
       </c>
       <c r="B435" t="n">
         <v>0.38</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-04-24 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-05-02 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>-0.09</v>
       </c>
     </row>
   </sheetData>
@@ -24619,28 +24793,28 @@
         <v>0.1454</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1746042856115565</v>
+        <v>-0.181713897591547</v>
       </c>
       <c r="J2" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="K2" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07735840274096362</v>
+        <v>0.08364904373021431</v>
       </c>
       <c r="M2" t="n">
-        <v>3.637879848350363</v>
+        <v>3.647811077601408</v>
       </c>
       <c r="N2" t="n">
-        <v>21.87719130284822</v>
+        <v>21.92636003529675</v>
       </c>
       <c r="O2" t="n">
-        <v>4.677305987729286</v>
+        <v>4.682559133134012</v>
       </c>
       <c r="P2" t="n">
-        <v>344.6780997094846</v>
+        <v>344.7507789230335</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24697,28 +24871,28 @@
         <v>0.1252</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1432020057345972</v>
+        <v>-0.1538602755129839</v>
       </c>
       <c r="J3" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="K3" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0497983093221035</v>
+        <v>0.05678376453168144</v>
       </c>
       <c r="M3" t="n">
-        <v>3.594154940853105</v>
+        <v>3.612539268274279</v>
       </c>
       <c r="N3" t="n">
-        <v>23.54266546726415</v>
+        <v>23.83578694415469</v>
       </c>
       <c r="O3" t="n">
-        <v>4.852078468786768</v>
+        <v>4.882190793501898</v>
       </c>
       <c r="P3" t="n">
-        <v>337.5514965951479</v>
+        <v>337.6604458958369</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24775,28 +24949,28 @@
         <v>0.1507</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.06209343667718335</v>
+        <v>-0.07185894759150845</v>
       </c>
       <c r="J4" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="K4" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008587447413373028</v>
+        <v>0.01147047355820718</v>
       </c>
       <c r="M4" t="n">
-        <v>3.73787390478101</v>
+        <v>3.743818971371466</v>
       </c>
       <c r="N4" t="n">
-        <v>26.78168803255307</v>
+        <v>26.97487242399515</v>
       </c>
       <c r="O4" t="n">
-        <v>5.175102707440025</v>
+        <v>5.193733957760559</v>
       </c>
       <c r="P4" t="n">
-        <v>333.4799221052928</v>
+        <v>333.579739351235</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -24853,28 +25027,28 @@
         <v>0.077</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.06917922527923066</v>
+        <v>-0.07949617376737793</v>
       </c>
       <c r="J5" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="K5" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0103398655839122</v>
+        <v>0.01359592489106975</v>
       </c>
       <c r="M5" t="n">
-        <v>3.971861606004833</v>
+        <v>3.98971990079581</v>
       </c>
       <c r="N5" t="n">
-        <v>27.55997383793003</v>
+        <v>27.79252148506867</v>
       </c>
       <c r="O5" t="n">
-        <v>5.249759407623365</v>
+        <v>5.271861292282705</v>
       </c>
       <c r="P5" t="n">
-        <v>334.7817645028742</v>
+        <v>334.8872161866248</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24931,28 +25105,28 @@
         <v>0.116</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04450323316027551</v>
+        <v>0.03625473535637833</v>
       </c>
       <c r="J6" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="K6" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="L6" t="n">
-        <v>0.005147113980466522</v>
+        <v>0.003431111571241541</v>
       </c>
       <c r="M6" t="n">
-        <v>3.78200805675207</v>
+        <v>3.796457201886155</v>
       </c>
       <c r="N6" t="n">
-        <v>23.03214760873387</v>
+        <v>23.14149221893461</v>
       </c>
       <c r="O6" t="n">
-        <v>4.799181972871405</v>
+        <v>4.810560489063058</v>
       </c>
       <c r="P6" t="n">
-        <v>333.4775179436943</v>
+        <v>333.5618294732371</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25009,28 +25183,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09847871275977099</v>
+        <v>0.09288152320001974</v>
       </c>
       <c r="J7" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="K7" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02240879477730096</v>
+        <v>0.02017392024954412</v>
       </c>
       <c r="M7" t="n">
-        <v>3.779172675024669</v>
+        <v>3.781971599784204</v>
       </c>
       <c r="N7" t="n">
-        <v>25.45538924381301</v>
+        <v>25.3984228744759</v>
       </c>
       <c r="O7" t="n">
-        <v>5.04533341255194</v>
+        <v>5.039684799119475</v>
       </c>
       <c r="P7" t="n">
-        <v>336.0543679737746</v>
+        <v>336.1115700682017</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25087,28 +25261,28 @@
         <v>0.1041</v>
       </c>
       <c r="I8" t="n">
-        <v>0.16453340723783</v>
+        <v>0.1626292111365467</v>
       </c>
       <c r="J8" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="K8" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04537881060874105</v>
+        <v>0.04498195376297887</v>
       </c>
       <c r="M8" t="n">
-        <v>4.279337562188522</v>
+        <v>4.254775819651344</v>
       </c>
       <c r="N8" t="n">
-        <v>34.26434020599295</v>
+        <v>34.03766588242866</v>
       </c>
       <c r="O8" t="n">
-        <v>5.853574993625088</v>
+        <v>5.834180823597145</v>
       </c>
       <c r="P8" t="n">
-        <v>333.3956362462725</v>
+        <v>333.4150796878657</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25165,28 +25339,28 @@
         <v>0.0634</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2683587936578869</v>
+        <v>0.2703584124845353</v>
       </c>
       <c r="J9" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="K9" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08444783534863343</v>
+        <v>0.08672594150305168</v>
       </c>
       <c r="M9" t="n">
-        <v>4.923688700834603</v>
+        <v>4.90022463781871</v>
       </c>
       <c r="N9" t="n">
-        <v>46.97669544721932</v>
+        <v>46.65747913221637</v>
       </c>
       <c r="O9" t="n">
-        <v>6.853954730461774</v>
+        <v>6.830628018873255</v>
       </c>
       <c r="P9" t="n">
-        <v>329.5873001973179</v>
+        <v>329.5668444664304</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25243,28 +25417,28 @@
         <v>0.07539999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2837156929152319</v>
+        <v>0.2901365959508619</v>
       </c>
       <c r="J10" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="K10" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="L10" t="n">
-        <v>0.08939237004584166</v>
+        <v>0.09403337407122392</v>
       </c>
       <c r="M10" t="n">
-        <v>5.120240453153913</v>
+        <v>5.123869839546991</v>
       </c>
       <c r="N10" t="n">
-        <v>49.33484623298256</v>
+        <v>49.16144043500653</v>
       </c>
       <c r="O10" t="n">
-        <v>7.023876866302722</v>
+        <v>7.011521977075058</v>
       </c>
       <c r="P10" t="n">
-        <v>333.263888843067</v>
+        <v>333.1982311406229</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -25321,28 +25495,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1535460968043453</v>
+        <v>0.1578454307690581</v>
       </c>
       <c r="J11" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="K11" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03334075514878609</v>
+        <v>0.03559474431343101</v>
       </c>
       <c r="M11" t="n">
-        <v>4.897830808413708</v>
+        <v>4.888727653003532</v>
       </c>
       <c r="N11" t="n">
-        <v>41.12744857921319</v>
+        <v>40.91919835938036</v>
       </c>
       <c r="O11" t="n">
-        <v>6.413068577460652</v>
+        <v>6.396811577604921</v>
       </c>
       <c r="P11" t="n">
-        <v>330.1794304621557</v>
+        <v>330.1354610242787</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -25399,28 +25573,28 @@
         <v>0.073</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.05349367415261746</v>
+        <v>-0.05092996385451765</v>
       </c>
       <c r="J12" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="K12" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="L12" t="n">
-        <v>0.002718213815988357</v>
+        <v>0.002497400778655567</v>
       </c>
       <c r="M12" t="n">
-        <v>6.076591463068009</v>
+        <v>6.053726524950188</v>
       </c>
       <c r="N12" t="n">
-        <v>63.16774262443602</v>
+        <v>62.80033000556432</v>
       </c>
       <c r="O12" t="n">
-        <v>7.947813700913983</v>
+        <v>7.924665923908989</v>
       </c>
       <c r="P12" t="n">
-        <v>332.0919631526033</v>
+        <v>332.0657053660652</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -25477,28 +25651,28 @@
         <v>0.0456</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.08361988117822587</v>
+        <v>-0.08732534279989364</v>
       </c>
       <c r="J13" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="K13" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="L13" t="n">
-        <v>0.004379322066651481</v>
+        <v>0.004839956699443149</v>
       </c>
       <c r="M13" t="n">
-        <v>7.767942581961575</v>
+        <v>7.732761740044757</v>
       </c>
       <c r="N13" t="n">
-        <v>95.64501595096715</v>
+        <v>95.04328732838505</v>
       </c>
       <c r="O13" t="n">
-        <v>9.779826989827946</v>
+        <v>9.74901468500202</v>
       </c>
       <c r="P13" t="n">
-        <v>330.9006119577177</v>
+        <v>330.9384477879263</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -25536,7 +25710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N409"/>
+  <dimension ref="A1:N412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54987,6 +55161,222 @@
         </is>
       </c>
     </row>
+    <row r="410">
+      <c r="A410" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-24 22:00:36+00:00</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>-41.189886606031436,175.99236405480752</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>-41.19051678425661,175.9920160814036</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>-41.1911631678362,175.9917508018326</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>-41.19182366838714,175.9915099041865</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>-41.1925042830242,175.99136962599457</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>-41.19319206492768,175.99129962596703</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>-41.19387698391538,175.9912812670994</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>-41.194554951806026,175.99130693737612</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>-41.19523503072869,175.9913846402585</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>-41.195918916934914,175.9914626781379</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>-41.19659664913146,175.9915639684159</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>-41.197269655080255,175.99169202478723</t>
+        </is>
+      </c>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02 22:00:18+00:00</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>-41.18988635731438,175.99236278613742</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>-41.19051569893427,175.9920105453383</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>-41.19116298694793,175.99174987914625</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>-41.19182303709731,175.99150606180953</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>-41.19250368511123,175.99136432257524</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>-41.193192204511774,175.99130236042066</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>-41.193876960657,175.99128734426804</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>-41.194554935320525,175.99130789042968</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>-41.1952340121839,175.99139624023235</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>-41.19591920481523,175.99146093176225</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>-41.19659461161523,175.99157557574716</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>-41.19727131511373,175.99168287066408</t>
+        </is>
+      </c>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:00:01+00:00</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>-41.1898833500979,175.99234744676303</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>-41.19051364134328,175.9920000498817</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>-41.19116221817274,175.99174595772928</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>-41.19182320926727,175.99150710973052</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>-41.19250367182427,175.99136420472146</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>-41.19319263540138,175.99131080156022</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>-41.193876868532385,175.99131141462215</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>-41.19455449845183,175.99133314634898</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>-41.195231050082775,175.99142997484773</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>-41.19591287144269,175.99149935202286</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>-41.19658265137194,175.9916437107658</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>-41.197260115127136,175.99174463201683</t>
+        </is>
+      </c>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0346/nzd0346.xlsx
+++ b/data/nzd0346/nzd0346.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N412"/>
+  <dimension ref="A1:N415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20226,6 +20226,150 @@
         <v>329.15</v>
       </c>
       <c r="N412" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-26 21:59:43+00:00</t>
+        </is>
+      </c>
+      <c r="B413" t="n">
+        <v>333.29</v>
+      </c>
+      <c r="C413" t="n">
+        <v>324.76</v>
+      </c>
+      <c r="D413" t="n">
+        <v>324.03</v>
+      </c>
+      <c r="E413" t="n">
+        <v>324.62</v>
+      </c>
+      <c r="F413" t="n">
+        <v>328.22</v>
+      </c>
+      <c r="G413" t="n">
+        <v>335.2</v>
+      </c>
+      <c r="H413" t="n">
+        <v>337.94</v>
+      </c>
+      <c r="I413" t="n">
+        <v>339.69</v>
+      </c>
+      <c r="J413" t="n">
+        <v>347.79</v>
+      </c>
+      <c r="K413" t="n">
+        <v>340.24</v>
+      </c>
+      <c r="L413" t="n">
+        <v>337.54</v>
+      </c>
+      <c r="M413" t="n">
+        <v>330.74</v>
+      </c>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-03 22:00:17+00:00</t>
+        </is>
+      </c>
+      <c r="B414" t="n">
+        <v>333</v>
+      </c>
+      <c r="C414" t="n">
+        <v>324.89</v>
+      </c>
+      <c r="D414" t="n">
+        <v>324.26</v>
+      </c>
+      <c r="E414" t="n">
+        <v>324.79</v>
+      </c>
+      <c r="F414" t="n">
+        <v>327.78</v>
+      </c>
+      <c r="G414" t="n">
+        <v>334.42</v>
+      </c>
+      <c r="H414" t="n">
+        <v>338.18</v>
+      </c>
+      <c r="I414" t="n">
+        <v>340.2</v>
+      </c>
+      <c r="J414" t="n">
+        <v>348.16</v>
+      </c>
+      <c r="K414" t="n">
+        <v>340.93</v>
+      </c>
+      <c r="L414" t="n">
+        <v>338.27</v>
+      </c>
+      <c r="M414" t="n">
+        <v>332.89</v>
+      </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:54:10+00:00</t>
+        </is>
+      </c>
+      <c r="B415" t="n">
+        <v>333.62</v>
+      </c>
+      <c r="C415" t="n">
+        <v>326.18</v>
+      </c>
+      <c r="D415" t="n">
+        <v>325.54</v>
+      </c>
+      <c r="E415" t="n">
+        <v>325.4</v>
+      </c>
+      <c r="F415" t="n">
+        <v>327.55</v>
+      </c>
+      <c r="G415" t="n">
+        <v>334.09</v>
+      </c>
+      <c r="H415" t="n">
+        <v>337.91</v>
+      </c>
+      <c r="I415" t="n">
+        <v>340.07</v>
+      </c>
+      <c r="J415" t="n">
+        <v>348.92</v>
+      </c>
+      <c r="K415" t="n">
+        <v>341.49</v>
+      </c>
+      <c r="L415" t="n">
+        <v>339.51</v>
+      </c>
+      <c r="M415" t="n">
+        <v>336.58</v>
+      </c>
+      <c r="N415" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20242,7 +20386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B438"/>
+  <dimension ref="A1:B441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24625,6 +24769,36 @@
       </c>
       <c r="B438" t="n">
         <v>-0.09</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-05-26 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-06-03 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>-0.63</v>
       </c>
     </row>
   </sheetData>
@@ -24793,28 +24967,28 @@
         <v>0.1454</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.181713897591547</v>
+        <v>-0.1902917752823896</v>
       </c>
       <c r="J2" t="n">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="K2" t="n">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08364904373021431</v>
+        <v>0.09104339454818711</v>
       </c>
       <c r="M2" t="n">
-        <v>3.647811077601408</v>
+        <v>3.666541341342997</v>
       </c>
       <c r="N2" t="n">
-        <v>21.92636003529675</v>
+        <v>22.074344842495</v>
       </c>
       <c r="O2" t="n">
-        <v>4.682559133134012</v>
+        <v>4.698334262533371</v>
       </c>
       <c r="P2" t="n">
-        <v>344.7507789230335</v>
+        <v>344.8387990719576</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24871,28 +25045,28 @@
         <v>0.1252</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1538602755129839</v>
+        <v>-0.164636197147385</v>
       </c>
       <c r="J3" t="n">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="K3" t="n">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05678376453168144</v>
+        <v>0.06413645639566756</v>
       </c>
       <c r="M3" t="n">
-        <v>3.612539268274279</v>
+        <v>3.632669969904242</v>
       </c>
       <c r="N3" t="n">
-        <v>23.83578694415469</v>
+        <v>24.14967551665398</v>
       </c>
       <c r="O3" t="n">
-        <v>4.882190793501898</v>
+        <v>4.914231935577927</v>
       </c>
       <c r="P3" t="n">
-        <v>337.6604458958369</v>
+        <v>337.7710157281759</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24949,28 +25123,28 @@
         <v>0.1507</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.07185894759150845</v>
+        <v>-0.08105005599503678</v>
       </c>
       <c r="J4" t="n">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="K4" t="n">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01147047355820718</v>
+        <v>0.01456685701140026</v>
       </c>
       <c r="M4" t="n">
-        <v>3.743818971371466</v>
+        <v>3.750648372135744</v>
       </c>
       <c r="N4" t="n">
-        <v>26.97487242399515</v>
+        <v>27.13445012947741</v>
       </c>
       <c r="O4" t="n">
-        <v>5.193733957760559</v>
+        <v>5.209073826456811</v>
       </c>
       <c r="P4" t="n">
-        <v>333.579739351235</v>
+        <v>333.674046180494</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25027,28 +25201,28 @@
         <v>0.077</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.07949617376737793</v>
+        <v>-0.08969919731507092</v>
       </c>
       <c r="J5" t="n">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="K5" t="n">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01359592489106975</v>
+        <v>0.01722780876908969</v>
       </c>
       <c r="M5" t="n">
-        <v>3.98971990079581</v>
+        <v>4.008027765085288</v>
       </c>
       <c r="N5" t="n">
-        <v>27.79252148506867</v>
+        <v>28.02547675186297</v>
       </c>
       <c r="O5" t="n">
-        <v>5.271861292282705</v>
+        <v>5.293909401554107</v>
       </c>
       <c r="P5" t="n">
-        <v>334.8872161866248</v>
+        <v>334.9919105603744</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25105,28 +25279,28 @@
         <v>0.116</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03625473535637833</v>
+        <v>0.02752918275282311</v>
       </c>
       <c r="J6" t="n">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="K6" t="n">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003431111571241541</v>
+        <v>0.001982820342719349</v>
       </c>
       <c r="M6" t="n">
-        <v>3.796457201886155</v>
+        <v>3.814125197875957</v>
       </c>
       <c r="N6" t="n">
-        <v>23.14149221893461</v>
+        <v>23.29133426506652</v>
       </c>
       <c r="O6" t="n">
-        <v>4.810560489063058</v>
+        <v>4.826109640804539</v>
       </c>
       <c r="P6" t="n">
-        <v>333.5618294732371</v>
+        <v>333.6513701861853</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25183,28 +25357,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09288152320001974</v>
+        <v>0.08761739695246429</v>
       </c>
       <c r="J7" t="n">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="K7" t="n">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02017392024954412</v>
+        <v>0.01816824487390933</v>
       </c>
       <c r="M7" t="n">
-        <v>3.781971599784204</v>
+        <v>3.783026853584613</v>
       </c>
       <c r="N7" t="n">
-        <v>25.3984228744759</v>
+        <v>25.33132294065388</v>
       </c>
       <c r="O7" t="n">
-        <v>5.039684799119475</v>
+        <v>5.033023240623262</v>
       </c>
       <c r="P7" t="n">
-        <v>336.1115700682017</v>
+        <v>336.1655936309944</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25261,28 +25435,28 @@
         <v>0.1041</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1626292111365467</v>
+        <v>0.1629411230288831</v>
       </c>
       <c r="J8" t="n">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="K8" t="n">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04498195376297887</v>
+        <v>0.04577792839426897</v>
       </c>
       <c r="M8" t="n">
-        <v>4.254775819651344</v>
+        <v>4.226314204408</v>
       </c>
       <c r="N8" t="n">
-        <v>34.03766588242866</v>
+        <v>33.79152656742189</v>
       </c>
       <c r="O8" t="n">
-        <v>5.834180823597145</v>
+        <v>5.81304795846567</v>
       </c>
       <c r="P8" t="n">
-        <v>333.4150796878657</v>
+        <v>333.411879246503</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25339,28 +25513,28 @@
         <v>0.0634</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2703584124845353</v>
+        <v>0.2744959388931765</v>
       </c>
       <c r="J9" t="n">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="K9" t="n">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08672594150305168</v>
+        <v>0.09022472680213034</v>
       </c>
       <c r="M9" t="n">
-        <v>4.90022463781871</v>
+        <v>4.890460147962036</v>
       </c>
       <c r="N9" t="n">
-        <v>46.65747913221637</v>
+        <v>46.39097278864994</v>
       </c>
       <c r="O9" t="n">
-        <v>6.830628018873255</v>
+        <v>6.811091894010089</v>
       </c>
       <c r="P9" t="n">
-        <v>329.5668444664304</v>
+        <v>329.524385426123</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25417,28 +25591,28 @@
         <v>0.07539999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2901365959508619</v>
+        <v>0.2996822495950387</v>
       </c>
       <c r="J10" t="n">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="K10" t="n">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="L10" t="n">
-        <v>0.09403337407122392</v>
+        <v>0.1003061345496086</v>
       </c>
       <c r="M10" t="n">
-        <v>5.123869839546991</v>
+        <v>5.147632638388164</v>
       </c>
       <c r="N10" t="n">
-        <v>49.16144043500653</v>
+        <v>49.18609951312595</v>
       </c>
       <c r="O10" t="n">
-        <v>7.011521977075058</v>
+        <v>7.013280224910876</v>
       </c>
       <c r="P10" t="n">
-        <v>333.1982311406229</v>
+        <v>333.1002726013564</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -25495,28 +25669,28 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1578454307690581</v>
+        <v>0.1663527887080425</v>
       </c>
       <c r="J11" t="n">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="K11" t="n">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03559474431343101</v>
+        <v>0.03965018287025868</v>
       </c>
       <c r="M11" t="n">
-        <v>4.888727653003532</v>
+        <v>4.90589025846147</v>
       </c>
       <c r="N11" t="n">
-        <v>40.91919835938036</v>
+        <v>40.92583169423311</v>
       </c>
       <c r="O11" t="n">
-        <v>6.396811577604921</v>
+        <v>6.397330044185082</v>
       </c>
       <c r="P11" t="n">
-        <v>330.1354610242787</v>
+        <v>330.0481563802659</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -25573,28 +25747,28 @@
         <v>0.073</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.05092996385451765</v>
+        <v>-0.04083279739457066</v>
       </c>
       <c r="J12" t="n">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="K12" t="n">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="L12" t="n">
-        <v>0.002497400778655567</v>
+        <v>0.001619141842067573</v>
       </c>
       <c r="M12" t="n">
-        <v>6.053726524950188</v>
+        <v>6.081962931200586</v>
       </c>
       <c r="N12" t="n">
-        <v>62.80033000556432</v>
+        <v>62.77441822618198</v>
       </c>
       <c r="O12" t="n">
-        <v>7.924665923908989</v>
+        <v>7.923030873736513</v>
       </c>
       <c r="P12" t="n">
-        <v>332.0657053660652</v>
+        <v>331.962083094972</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -25651,28 +25825,28 @@
         <v>0.0456</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.08732534279989364</v>
+        <v>-0.08104601734115496</v>
       </c>
       <c r="J13" t="n">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="K13" t="n">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="L13" t="n">
-        <v>0.004839956699443149</v>
+        <v>0.004223450981322485</v>
       </c>
       <c r="M13" t="n">
-        <v>7.732761740044757</v>
+        <v>7.71300468287697</v>
       </c>
       <c r="N13" t="n">
-        <v>95.04328732838505</v>
+        <v>94.56074207684445</v>
       </c>
       <c r="O13" t="n">
-        <v>9.74901468500202</v>
+        <v>9.724234781042899</v>
       </c>
       <c r="P13" t="n">
-        <v>330.9384477879263</v>
+        <v>330.8739823849118</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -25710,7 +25884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N412"/>
+  <dimension ref="A1:N415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55377,6 +55551,222 @@
         </is>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-26 21:59:43+00:00</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>-41.189882377839474,175.99234248741672</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>-41.19051330217983,175.99199831986144</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>-41.19116185639615,175.99174411235666</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>-41.19182231015734,175.9915016372543</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>-41.192503592102526,175.99136349759888</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>-41.19319275070976,175.99131306045675</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>-41.19387686533986,175.99131224874333</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>-41.194554502573254,175.9913329080856</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>-41.19523118519638,175.99142843607586</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>-41.195911796687305,175.99150587182388</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>-41.19658122510519,175.99165183589398</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>-41.19725677403666,175.99176305613074</t>
+        </is>
+      </c>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-03 22:00:17+00:00</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>-41.18988172213019,175.99233914274137</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>-41.19051359612149,175.99199981921234</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>-41.19116237645,175.99174676507982</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>-41.19182263536735,175.99150361666057</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>-41.19250300747624,175.9913583120334</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>-41.19319227733823,175.99130378709214</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>-41.19387685439401,175.99131510858737</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>-41.19455439747667,175.99133898380194</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>-41.19523080064223,175.99143281565728</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>-41.19591047243464,175.99151390514976</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>-41.196579737712135,175.99166030924152</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>-41.197252256205324,175.99178796923752</t>
+        </is>
+      </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:54:10+00:00</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>-41.189883123991315,175.9923462934267</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>-41.19051651292605,175.99201469738728</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>-41.191165270661664,175.99176152806183</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>-41.19182380229709,175.9915107192362</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>-41.192502701876045,175.99135560139692</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>-41.193192077065426,175.99129986374558</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>-41.19387686670809,175.99131189126282</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>-41.19455442426602,175.99133743508992</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>-41.19523001074673,175.991441811554</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>-41.195909397678456,175.9915204249502</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>-41.19657721118004,175.99167470232408</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>-41.19724450233364,175.99183072707248</t>
+        </is>
+      </c>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
